--- a/qc/MTPE_QC_기록부.xlsx
+++ b/qc/MTPE_QC_기록부.xlsx
@@ -1208,7 +1208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1749,13 +1749,13 @@
       <c r="F35" s="17" t="n"/>
     </row>
     <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="19" t="n"/>
+      <c r="A36" s="18" t="n"/>
       <c r="B36" s="12" t="n">
         <v>5</v>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>[+ 새 작품/언어]로 빈 5단계 템플릿을 만들 수 있다</t>
+          <t>[+ 새 작품 만들기 (v1)]를 누르면 그 작품이 v1으로 즉시 생성되고 번역 탭 목록에도 바로 보인다</t>
         </is>
       </c>
       <c r="D36" s="10" t="n"/>
@@ -1763,17 +1763,13 @@
       <c r="F36" s="17" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t>프롬프트 다듬기 ⭐</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>샘플 회차+모델 고르고 [시험 실행]하면 단계별 결과가 뜬다</t>
+      <c r="A37" s="19" t="n"/>
+      <c r="B37" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>이미 있는 작품·언어를 다시 만들려 하면 경고가 뜬다(덮어쓰기 방지)</t>
         </is>
       </c>
       <c r="D37" s="10" t="n"/>
@@ -1781,13 +1777,17 @@
       <c r="F37" s="17" t="n"/>
     </row>
     <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="18" t="n"/>
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>프롬프트 다듬기 ⭐</t>
+        </is>
+      </c>
       <c r="B38" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Gemini로 시험 실행하면 진짜 결과가 단계별로 나온다</t>
+          <t>샘플 회차+모델 고르고 [시험 실행]하면 단계별 결과가 뜬다</t>
         </is>
       </c>
       <c r="D38" s="10" t="n"/>
@@ -1797,11 +1797,11 @@
     <row r="39" ht="26" customHeight="1">
       <c r="A39" s="18" t="n"/>
       <c r="B39" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>글 고치고 [이 단계부터 다시] 누르면 그 단계만 다시 돌고 반영된다</t>
+          <t>Gemini로 시험 실행하면 진짜 결과가 단계별로 나온다</t>
         </is>
       </c>
       <c r="D39" s="10" t="n"/>
@@ -1811,11 +1811,11 @@
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="18" t="n"/>
       <c r="B40" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>[실제 보낸 프롬프트 보기]로 합쳐진 지시문이 보인다</t>
+          <t>글 고치고 [이 단계부터 다시] 누르면 그 단계만 다시 돌고 반영된다</t>
         </is>
       </c>
       <c r="D40" s="10" t="n"/>
@@ -1823,13 +1823,13 @@
       <c r="F40" s="17" t="n"/>
     </row>
     <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="19" t="n"/>
+      <c r="A41" s="18" t="n"/>
       <c r="B41" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>다듬은 뒤 저장하면 번역 탭에 반영된다</t>
+          <t>[실제 보낸 프롬프트 보기]로 합쳐진 지시문이 보인다</t>
         </is>
       </c>
       <c r="D41" s="10" t="n"/>
@@ -1837,17 +1837,13 @@
       <c r="F41" s="17" t="n"/>
     </row>
     <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>이상 상황 / 안 죽는지</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>틀린/만료된 키로 하면 알아볼 에러 메시지가 뜬다(안 꺼짐)</t>
+      <c r="A42" s="19" t="n"/>
+      <c r="B42" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>다듬은 뒤 저장하면 번역 탭에 반영된다</t>
         </is>
       </c>
       <c r="D42" s="10" t="n"/>
@@ -1855,13 +1851,17 @@
       <c r="F42" s="17" t="n"/>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="18" t="n"/>
+      <c r="A43" s="15" t="inlineStr">
+        <is>
+          <t>이상 상황 / 안 죽는지</t>
+        </is>
+      </c>
       <c r="B43" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>회차 안 고르고 번역하면 안내 메시지가 뜬다</t>
+          <t>틀린/만료된 키로 하면 알아볼 에러 메시지가 뜬다(안 꺼짐)</t>
         </is>
       </c>
       <c r="D43" s="10" t="n"/>
@@ -1871,11 +1871,11 @@
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="18" t="n"/>
       <c r="B44" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>아주 긴 원문/빈 파일을 넣어도 어떻게든 처리/안내된다</t>
+          <t>회차 안 고르고 번역하면 안내 메시지가 뜬다</t>
         </is>
       </c>
       <c r="D44" s="10" t="n"/>
@@ -1883,13 +1883,13 @@
       <c r="F44" s="17" t="n"/>
     </row>
     <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="19" t="n"/>
+      <c r="A45" s="18" t="n"/>
       <c r="B45" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>번역 도중 다른 탭으로 옮기거나 다시 해도 안 깨진다</t>
+          <t>아주 긴 원문/빈 파일을 넣어도 어떻게든 처리/안내된다</t>
         </is>
       </c>
       <c r="D45" s="10" t="n"/>
@@ -1897,17 +1897,13 @@
       <c r="F45" s="17" t="n"/>
     </row>
     <row r="46" ht="26" customHeight="1">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>껐다 켜도 유지</t>
-        </is>
-      </c>
+      <c r="A46" s="19" t="n"/>
       <c r="B46" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>앱을 껐다 켜도 고쳐둔 프롬프트가 남아 있다</t>
+          <t>번역 도중 다른 탭으로 옮기거나 다시 해도 안 깨진다</t>
         </is>
       </c>
       <c r="D46" s="10" t="n"/>
@@ -1915,13 +1911,17 @@
       <c r="F46" s="17" t="n"/>
     </row>
     <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="18" t="n"/>
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>껐다 켜도 유지</t>
+        </is>
+      </c>
       <c r="B47" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>회차 목록·TB·시트 선택이 다시 켜도 유지된다</t>
+          <t>앱을 껐다 켜도 고쳐둔 프롬프트가 남아 있다</t>
         </is>
       </c>
       <c r="D47" s="10" t="n"/>
@@ -1929,13 +1929,13 @@
       <c r="F47" s="17" t="n"/>
     </row>
     <row r="48" ht="26" customHeight="1">
-      <c r="A48" s="19" t="n"/>
+      <c r="A48" s="18" t="n"/>
       <c r="B48" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>번역 결과(final.txt)가 보관된다</t>
+          <t>회차 목록·TB·시트 선택이 다시 켜도 유지된다</t>
         </is>
       </c>
       <c r="D48" s="10" t="n"/>
@@ -1943,17 +1943,13 @@
       <c r="F48" s="17" t="n"/>
     </row>
     <row r="49" ht="26" customHeight="1">
-      <c r="A49" s="15" t="inlineStr">
-        <is>
-          <t>평가표 ⭐ (한→영·한→일)</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>번역 후 [평가 시트 생성] 버튼이 보인다</t>
+      <c r="A49" s="19" t="n"/>
+      <c r="B49" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>번역 결과(final.txt)가 보관된다</t>
         </is>
       </c>
       <c r="D49" s="10" t="n"/>
@@ -1961,13 +1957,17 @@
       <c r="F49" s="17" t="n"/>
     </row>
     <row r="50" ht="26" customHeight="1">
-      <c r="A50" s="18" t="n"/>
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>평가표 ⭐ (한→영·한→일)</t>
+        </is>
+      </c>
       <c r="B50" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>(중→한 작품) 평가표 버튼이 안 보인다(정상)</t>
+          <t>번역 후 [평가 시트 생성] 버튼이 보인다</t>
         </is>
       </c>
       <c r="D50" s="10" t="n"/>
@@ -1977,11 +1977,11 @@
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="18" t="n"/>
       <c r="B51" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>[평가 시트 생성]하면 엑셀이 생기고 다운로드/폴더 열기가 된다</t>
+          <t>(중→한 작품) 평가표 버튼이 안 보인다(정상)</t>
         </is>
       </c>
       <c r="D51" s="10" t="n"/>
@@ -1991,11 +1991,11 @@
     <row r="52" ht="26" customHeight="1">
       <c r="A52" s="18" t="n"/>
       <c r="B52" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>평가표에 원문·번역이 채워지고 표 안 계산이 안 깨진다</t>
+          <t>[평가 시트 생성]하면 엑셀이 생기고 다운로드/폴더 열기가 된다</t>
         </is>
       </c>
       <c r="D52" s="10" t="n"/>
@@ -2005,11 +2005,11 @@
     <row r="53" ht="26" customHeight="1">
       <c r="A53" s="18" t="n"/>
       <c r="B53" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>장면 설명, 버전·날짜 등이 표시된다</t>
+          <t>평가표에 원문·번역이 채워지고 표 안 계산이 안 깨진다</t>
         </is>
       </c>
       <c r="D53" s="10" t="n"/>
@@ -2019,11 +2019,11 @@
     <row r="54" ht="26" customHeight="1">
       <c r="A54" s="18" t="n"/>
       <c r="B54" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>샘플 문장이 채워지고 채점칸은 비어 있다(직접 채점용)</t>
+          <t>장면 설명, 버전·날짜 등이 표시된다</t>
         </is>
       </c>
       <c r="D54" s="10" t="n"/>
@@ -2031,36 +2031,50 @@
       <c r="F54" s="17" t="n"/>
     </row>
     <row r="55" ht="26" customHeight="1">
-      <c r="A55" s="19" t="n"/>
+      <c r="A55" s="18" t="n"/>
       <c r="B55" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>[평가 시트 생성]하면 평가표가 1부만 생성된다</t>
+          <t>샘플 문장이 채워지고 채점칸은 비어 있다(직접 채점용)</t>
         </is>
       </c>
       <c r="D55" s="10" t="n"/>
       <c r="E55" s="16" t="n"/>
       <c r="F55" s="17" t="n"/>
     </row>
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="19" t="n"/>
+      <c r="B56" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>[평가 시트 생성]하면 평가표가 1부만 생성된다</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="16" t="n"/>
+      <c r="F56" s="17" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A43:A46"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A38:A42"/>
     <mergeCell ref="A16:A20"/>
     <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A42:A45"/>
     <mergeCell ref="A21:A24"/>
-    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="A47:A49"/>
     <mergeCell ref="A11:A15"/>
-    <mergeCell ref="A49:A55"/>
-    <mergeCell ref="A37:A41"/>
-    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="A50:A56"/>
+    <mergeCell ref="A32:A37"/>
     <mergeCell ref="A6:A10"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="D3:D55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D3:D56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✅ 잘 됨,❌ 안 됨,⏭ 아직 안 해봄,— 해당 없음"</formula1>
     </dataValidation>
   </dataValidations>
